--- a/jogos_2025-02-17.xlsx
+++ b/jogos_2025-02-17.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.01</v>
+        <v>2.7</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.29</v>
       </c>
       <c r="N4" t="n">
-        <v>3.64</v>
+        <v>2.53</v>
       </c>
       <c r="O4" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="T4" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V4" t="n">
         <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['10', '51']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>['7', '41', '55']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.69</v>
+        <v>1.38</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.63</v>
+        <v>1.9</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45705.375</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,109 +1030,109 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S5" t="n">
         <v>3</v>
       </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.89</v>
-      </c>
       <c r="T5" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
         <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['10', '51']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['7', '41', '55']</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.38</v>
+        <v>1.69</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45705.375</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Adanaspor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1174,7 +1174,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.66</v>
+        <v>2.78</v>
       </c>
       <c r="M6" t="n">
-        <v>3.59</v>
+        <v>3.37</v>
       </c>
       <c r="N6" t="n">
-        <v>5.3</v>
+        <v>2.44</v>
       </c>
       <c r="O6" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.33</v>
       </c>
-      <c r="S6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AC6" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI6" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['34']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['89']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45705.45833333334</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Adanaspor</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1303,7 +1303,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.78</v>
+        <v>1.66</v>
       </c>
       <c r="M7" t="n">
-        <v>3.37</v>
+        <v>3.59</v>
       </c>
       <c r="N7" t="n">
-        <v>2.44</v>
+        <v>5.3</v>
       </c>
       <c r="O7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA7" t="n">
         <v>3.4</v>
       </c>
-      <c r="P7" t="n">
+      <c r="AB7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD7" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>2.75</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['85']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['49']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45705.45833333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P10" t="n">
         <v>2.2</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q10" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.4</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W10" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="X10" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.68</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45705.54166666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.77</v>
+        <v>2.2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.04</v>
+        <v>3.19</v>
       </c>
       <c r="N11" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P11" t="n">
         <v>2.1</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>3.75</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.63</v>
-      </c>
       <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.36</v>
       </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="X11" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AC11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI11" t="n">
         <v>1.73</v>
       </c>
-      <c r="AD11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['30']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45705.54166666666</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Şanlıurfaspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.59</v>
+        <v>4.71</v>
       </c>
       <c r="M14" t="n">
-        <v>3.91</v>
+        <v>4.26</v>
       </c>
       <c r="N14" t="n">
-        <v>5.26</v>
+        <v>1.62</v>
       </c>
       <c r="O14" t="n">
-        <v>1.91</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>7</v>
+        <v>2.15</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X14" t="n">
-        <v>3.75</v>
+        <v>5.17</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.88</v>
+        <v>1.49</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.1</v>
+        <v>2.26</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['47', '86']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.8</v>
+        <v>1.22</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45705.58333333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.71</v>
+        <v>1.29</v>
       </c>
       <c r="M15" t="n">
-        <v>4.26</v>
+        <v>6.34</v>
       </c>
       <c r="N15" t="n">
-        <v>1.62</v>
+        <v>5.56</v>
       </c>
       <c r="O15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
         <v>4.5</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.15</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="X15" t="n">
-        <v>5.17</v>
+        <v>2.95</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.55</v>
+        <v>1.73</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.26</v>
+        <v>3.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="AC15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AI15" t="n">
         <v>1.53</v>
       </c>
-      <c r="AD15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['54']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['47', '86']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45705.58333333334</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.69</v>
+        <v>5.1</v>
       </c>
       <c r="M16" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P16" t="n">
         <v>1.98</v>
       </c>
-      <c r="N16" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q16" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.6</v>
+        <v>4.56</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['45+4']</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45705.58333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,19 +2578,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Şanlıurfaspor</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="M17" t="n">
-        <v>6.34</v>
+        <v>3.91</v>
       </c>
       <c r="N17" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="O17" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AI17" t="n">
         <v>1.4</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['16']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45705.58333333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,91 +2707,91 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="Y18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC18" t="n">
         <v>2.5</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AD18" t="n">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['21', '23']</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.73</v>
+        <v>2.55</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45705.58333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.1</v>
+        <v>2.24</v>
       </c>
       <c r="M19" t="n">
-        <v>3.41</v>
+        <v>2.07</v>
       </c>
       <c r="N19" t="n">
-        <v>1.72</v>
+        <v>5.57</v>
       </c>
       <c r="O19" t="n">
-        <v>5.25</v>
+        <v>3.25</v>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.5</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['21', '23']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.28</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['45+2']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AI19" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45705.58333333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.37</v>
+        <v>2.69</v>
       </c>
       <c r="M20" t="n">
-        <v>2.62</v>
+        <v>1.98</v>
       </c>
       <c r="N20" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="O20" t="n">
         <v>3.75</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.1</v>
-      </c>
       <c r="P20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q20" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>3.15</v>
-      </c>
       <c r="Z20" t="n">
-        <v>1.31</v>
+        <v>1.91</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+4']</t>
         </is>
       </c>
       <c r="AG20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.28</v>
       </c>
-      <c r="AH20" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AI20" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.55</v>
+        <v>1.73</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45705.58333333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.34</v>
+        <v>2.05</v>
       </c>
       <c r="M21" t="n">
-        <v>3.53</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P21" t="n">
         <v>2.05</v>
       </c>
-      <c r="O21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="T21" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="X21" t="n">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['46']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['23', '29']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.38</v>
+        <v>1.72</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45705.625</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3238,7 +3238,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.05</v>
+        <v>4.33</v>
       </c>
       <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S22" t="n">
         <v>3.1</v>
       </c>
-      <c r="N22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.63</v>
-      </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="X22" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>2.04</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.67</v>
+        <v>2.67</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.5</v>
+        <v>1.49</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45705.625</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>3.53</v>
       </c>
       <c r="N23" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="O23" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AC23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['23', '29']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['8']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['21']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.49</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45705.625</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Caldiero Terme</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
         <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,55 +4023,55 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="M28" t="n">
-        <v>3.39</v>
+        <v>3.18</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S28" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="T28" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="X28" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="Y28" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AC28" t="n">
         <v>2</v>
@@ -4081,25 +4081,25 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['1', '9', '27', '52', '87']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['52', '90+1']</t>
+          <t>['17', '90+5']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45705.6875</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Lucchese</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Caldiero Terme</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -4152,28 +4152,28 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.19</v>
+        <v>2.94</v>
       </c>
       <c r="M29" t="n">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="N29" t="n">
-        <v>3.35</v>
+        <v>2.53</v>
       </c>
       <c r="O29" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P29" t="n">
         <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T29" t="n">
         <v>3.5</v>
@@ -4185,19 +4185,19 @@
         <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X29" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AB29" t="n">
         <v>1.21</v>
@@ -4210,25 +4210,25 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['1', '9', '27', '52', '87']</t>
+          <t>['51', '70']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['17', '90+5']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45705.6875</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,16 +4255,16 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lucchese</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -4273,7 +4273,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.94</v>
+        <v>2.18</v>
       </c>
       <c r="M30" t="n">
-        <v>2.99</v>
+        <v>3.21</v>
       </c>
       <c r="N30" t="n">
-        <v>2.53</v>
+        <v>3.78</v>
       </c>
       <c r="O30" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
+        <v>4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T30" t="n">
         <v>3.25</v>
       </c>
-      <c r="R30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U30" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W30" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="X30" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['51', '70']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45705.6875</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,22 +4384,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4410,22 +4410,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="M31" t="n">
-        <v>3.21</v>
+        <v>3.39</v>
       </c>
       <c r="N31" t="n">
-        <v>3.78</v>
+        <v>4.3</v>
       </c>
       <c r="O31" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="R31" t="n">
         <v>1.44</v>
@@ -4440,53 +4440,53 @@
         <v>1.33</v>
       </c>
       <c r="V31" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="X31" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['52', '90+1']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45705.6875</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,22 +4513,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4539,22 +4539,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="M32" t="n">
-        <v>3.47</v>
+        <v>3.19</v>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>2.99</v>
       </c>
       <c r="O32" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="P32" t="n">
         <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
         <v>1.44</v>
@@ -4569,35 +4569,35 @@
         <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="X32" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="Y32" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="n">
         <v>1.91</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['82', '86']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45705.69791666666</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,22 +4642,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4668,22 +4668,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.19</v>
+        <v>3.47</v>
       </c>
       <c r="N33" t="n">
-        <v>2.99</v>
+        <v>4</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="P33" t="n">
         <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="R33" t="n">
         <v>1.44</v>
@@ -4698,35 +4698,35 @@
         <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W33" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="X33" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AD33" t="n">
         <v>1.91</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['82', '86']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45705.69791666666</v>
@@ -4761,119 +4761,119 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M34" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="N34" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X34" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD34" t="n">
         <v>2</v>
       </c>
-      <c r="H34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>4</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['84', '90+5']</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.52</v>
+        <v>4.1</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.91</v>
+        <v>1.2</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45705.70833333334</v>
@@ -4890,35 +4890,35 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.19</v>
+        <v>2.6</v>
       </c>
       <c r="M35" t="n">
-        <v>7.51</v>
+        <v>2.75</v>
       </c>
       <c r="N35" t="n">
-        <v>12.03</v>
+        <v>3.3</v>
       </c>
       <c r="O35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W35" t="n">
         <v>1.57</v>
       </c>
-      <c r="P35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.08</v>
-      </c>
       <c r="X35" t="n">
-        <v>8</v>
+        <v>2.25</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.3</v>
+        <v>2.88</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.77</v>
+        <v>5.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>1.14</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['84', '90+5']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="AH35" t="n">
-        <v>4.1</v>
+        <v>1.52</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.2</v>
+        <v>1.91</v>
       </c>
       <c r="AJ35" t="n">
-        <v>4.33</v>
+        <v>2.4</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45705.70833333334</v>
